--- a/artfynd/A 34930-2022 artfynd.xlsx
+++ b/artfynd/A 34930-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34930-2022 artfynd.xlsx
+++ b/artfynd/A 34930-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92498248</v>
+        <v>76896553</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Späd bäckmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Campylophyllum montanum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lindb.) B.H.Allen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käringbäcken, Vrm</t>
+          <t>Käringbäcken, delpop 1 (HmUE14), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411837.2208547291</v>
+        <v>411875</v>
       </c>
       <c r="R2" t="n">
-        <v>6683522.968053894</v>
+        <v>6683606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Med kapslar!</t>
+          <t>Ny bäck med arten! Äldre men relativt likåldrig granskog. Eftersökt utmed ca 200 m.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +770,14 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Lövrik barrskog vid skogsbäck</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Större platt block eller mindre häll</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,19 +791,18 @@
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>92498398</v>
       </c>
       <c r="B3" t="n">
-        <v>94653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411837.2208547291</v>
+        <v>411837</v>
       </c>
       <c r="R3" t="n">
-        <v>6683522.968053894</v>
+        <v>6683523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +867,9 @@
           <t>2015-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99663882</v>
+        <v>92498248</v>
       </c>
       <c r="B4" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,19 +930,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Käringbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411831.4517588177</v>
+        <v>411837</v>
       </c>
       <c r="R4" t="n">
-        <v>6683531.046819903</v>
+        <v>6683523</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Med kapslar!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövrik äldre barrskog vid liten skogsbäck</t>
+          <t>Lövrik barrskog vid skogsbäck</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,6 +1010,210 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99663882</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Käringbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411831</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683531</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik äldre barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>99663877</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Käringbäcken, nedströms grusvägen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411875</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683606</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik äldre barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34930-2022 artfynd.xlsx
+++ b/artfynd/A 34930-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76896553</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99663882</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,8 +1239,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99663877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>